--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D2C673-CCE8-4ADB-9D48-C8F445A7B07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD183828-25A4-4EF6-8B36-23B2D806412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -260,10 +260,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,FirstHitOnly,2,0,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.EffectTriggerPolicy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -368,27 +364,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>艾莲乔_普通攻击_3_霜冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲乔_冲刺攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>艾莲乔_特殊冲刺攻击_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾莲乔_特殊冲刺攻击_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲乔_特殊技_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>艾莲乔_特殊技_2_强化</t>
+    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,FirstHitOnly,1,0,1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,FirstHitOnly,3,0,1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_普通攻击_1_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_普通攻击_2_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_普通攻击_3_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_特殊冲刺攻击_无蓄力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_特殊冲刺攻击_蓄力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_冲刺攻击_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_特殊技_1_强化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_特殊技_2_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute,Attacker,FirstHitOnly,1,0,1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔_通用_急冻充能+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,20,10,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -797,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="24.125" customWidth="1"/>
@@ -825,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
         <v>16</v>
@@ -906,7 +938,7 @@
         <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -914,13 +946,13 @@
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>1010000</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
@@ -943,7 +975,7 @@
         <v>1010001</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
@@ -966,7 +998,7 @@
         <v>1010002</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -989,7 +1021,7 @@
         <v>1010003</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -1003,7 +1035,7 @@
         <v>1010004</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -1029,7 +1061,7 @@
         <v>1010005</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -1052,7 +1084,7 @@
         <v>1010006</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -1075,7 +1107,7 @@
         <v>1010007</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -1101,7 +1133,7 @@
         <v>1010008</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -1118,13 +1150,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14">
         <v>1020000</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -1150,7 +1182,7 @@
         <v>1020001</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s">
         <v>54</v>
@@ -1173,7 +1205,7 @@
         <v>1020002</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
@@ -1187,7 +1219,7 @@
         <v>1020003</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
         <v>54</v>
@@ -1201,7 +1233,7 @@
         <v>1020004</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
@@ -1215,7 +1247,7 @@
         <v>1020005</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
         <v>54</v>
@@ -1229,7 +1261,7 @@
         <v>1020006</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -1243,7 +1275,7 @@
         <v>1020007</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
@@ -1257,7 +1289,7 @@
         <v>1020008</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
@@ -1265,13 +1297,13 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C23">
         <v>1040000</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
         <v>54</v>
@@ -1279,13 +1311,13 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24">
         <v>1040001</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
         <v>54</v>
@@ -1299,7 +1331,7 @@
         <v>1040002</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
         <v>54</v>
@@ -1313,7 +1345,7 @@
         <v>1040003</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
         <v>54</v>
@@ -1327,7 +1359,7 @@
         <v>1040004</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
@@ -1341,7 +1373,7 @@
         <v>1040005</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
@@ -1355,7 +1387,7 @@
         <v>1040006</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
         <v>54</v>
@@ -1369,7 +1401,7 @@
         <v>1040007</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
         <v>54</v>
@@ -1383,10 +1415,80 @@
         <v>1040008</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32">
+        <v>1040009</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33">
+        <v>1040010</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34">
+        <v>1040011</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35">
+        <v>1040012</v>
+      </c>
+      <c r="D35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>1040013</v>
+      </c>
+      <c r="D36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD183828-25A4-4EF6-8B36-23B2D806412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F30C0B-8FC4-48CA-B255-73BBD7DE4677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -249,13 +249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,EveryHit,10,0,200</t>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,EveryHit,10,0,200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FirstHitOnly</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -421,6 +414,13 @@
   </si>
   <si>
     <t>Damage,Victim,EveryHit,20,10,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,EveryHit,5,0,200</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,EveryHit,5,0,200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -857,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G1" t="s">
         <v>16</v>
@@ -938,7 +938,7 @@
         <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -946,16 +946,16 @@
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>1010000</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
@@ -975,10 +975,10 @@
         <v>1010001</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -998,10 +998,10 @@
         <v>1010002</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -1021,10 +1021,10 @@
         <v>1010003</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1035,10 +1035,10 @@
         <v>1010004</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>18</v>
@@ -1061,10 +1061,10 @@
         <v>1010005</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="I10" t="s">
         <v>53</v>
@@ -1084,10 +1084,10 @@
         <v>1010006</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
         <v>40</v>
@@ -1107,10 +1107,10 @@
         <v>1010007</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>21</v>
@@ -1133,10 +1133,10 @@
         <v>1010008</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
         <v>44</v>
@@ -1150,16 +1150,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>1020000</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>46</v>
@@ -1182,13 +1182,13 @@
         <v>1020001</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" t="s">
         <v>54</v>
-      </c>
-      <c r="I15" t="s">
-        <v>56</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1205,10 +1205,10 @@
         <v>1020002</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -1219,10 +1219,10 @@
         <v>1020003</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -1233,10 +1233,10 @@
         <v>1020004</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
@@ -1247,10 +1247,10 @@
         <v>1020005</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -1261,10 +1261,10 @@
         <v>1020006</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -1275,10 +1275,10 @@
         <v>1020007</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -1289,38 +1289,38 @@
         <v>1020008</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23">
         <v>1040000</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24">
         <v>1040001</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -1331,10 +1331,10 @@
         <v>1040002</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
@@ -1345,10 +1345,10 @@
         <v>1040003</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
@@ -1359,10 +1359,10 @@
         <v>1040004</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
@@ -1373,10 +1373,10 @@
         <v>1040005</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -1387,10 +1387,10 @@
         <v>1040006</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
@@ -1401,10 +1401,10 @@
         <v>1040007</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
@@ -1415,10 +1415,10 @@
         <v>1040008</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
@@ -1429,10 +1429,10 @@
         <v>1040009</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
@@ -1443,10 +1443,10 @@
         <v>1040010</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
@@ -1457,10 +1457,10 @@
         <v>1040011</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
@@ -1471,10 +1471,10 @@
         <v>1040012</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
@@ -1485,10 +1485,10 @@
         <v>1040013</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F30C0B-8FC4-48CA-B255-73BBD7DE4677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64548B30-4E15-4899-8B2D-00D379FEB786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="60">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,155 +88,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>##remark1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>ZZZ.HitEffectType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果类型</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>ZZZ.EffectTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>作用目标</t>
-  </si>
-  <si>
-    <t>Policy</t>
-  </si>
-  <si>
-    <t>触发策略</t>
-  </si>
-  <si>
-    <t>Param1</t>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Param2</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>参数2 (喧响值 / 备用)</t>
-  </si>
-  <si>
-    <t>Param3</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数3 (目标AttributeId / 要挂的BuffId)</t>
-  </si>
-  <si>
-    <t>##remark2</t>
-  </si>
-  <si>
-    <t>##remark3</t>
-  </si>
-  <si>
-    <t>##remark4</t>
-  </si>
-  <si>
-    <t>##remark5</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>造成伤害</t>
-  </si>
-  <si>
-    <t>修改属性(如回血/回能)</t>
-  </si>
-  <si>
-    <t>ApplyBuff</t>
-  </si>
-  <si>
-    <t>施加Buff</t>
-  </si>
-  <si>
-    <t>Victim</t>
-  </si>
-  <si>
-    <t>受击者</t>
-  </si>
-  <si>
-    <t>Attacker</t>
-  </si>
-  <si>
-    <t>攻击者自身</t>
-  </si>
-  <si>
-    <t>ZZZ.EffectTriggerPolicy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EveryHit</t>
-  </si>
-  <si>
-    <t>每次命中触发</t>
-  </si>
-  <si>
-    <t>仅首次命中触发</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>属性变化量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -245,18 +96,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ModifyAttribute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FirstHitOnly</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZZZ.EffectTriggerPolicy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>effects#sep=|</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -365,14 +204,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,FirstHitOnly,1,0,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,FirstHitOnly,3,0,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲乔_普通攻击_1_急冻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -405,22 +236,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ModifyAttribute,Attacker,FirstHitOnly,1,0,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲乔_通用_急冻充能+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,20,10,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,EveryHit,5,0,200</t>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,20,10,0|ModifyAttribute,Attacker,EveryHit,5,0,200</t>
+    <t>Damage,Victim,EveryHit,None,20,0,1</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,7 +266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,24 +291,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF292929"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF292929"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -509,10 +333,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -834,7 +658,7 @@
   <cols>
     <col min="4" max="4" width="24.125" customWidth="1"/>
     <col min="5" max="5" width="39.625" customWidth="1"/>
-    <col min="6" max="6" width="71.875" customWidth="1"/>
+    <col min="6" max="6" width="91.125" customWidth="1"/>
     <col min="9" max="9" width="17.125" customWidth="1"/>
     <col min="10" max="10" width="13.875" customWidth="1"/>
     <col min="11" max="11" width="29.375" customWidth="1"/>
@@ -857,22 +681,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -891,29 +700,15 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I2" s="1"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="I3" s="1"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -926,46 +721,32 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="I4" s="1"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>1010000</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
@@ -975,20 +756,13 @@
         <v>1010001</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
@@ -998,20 +772,13 @@
         <v>1010002</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
@@ -1021,10 +788,10 @@
         <v>1010003</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1035,23 +802,13 @@
         <v>1010004</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
@@ -1061,20 +818,12 @@
         <v>1010005</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
@@ -1084,20 +833,12 @@
         <v>1010006</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
@@ -1107,23 +848,13 @@
         <v>1010007</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
@@ -1133,46 +864,28 @@
         <v>1010008</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>1020000</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
@@ -1182,20 +895,12 @@
         <v>1020001</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
@@ -1205,10 +910,10 @@
         <v>1020002</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -1219,10 +924,10 @@
         <v>1020003</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -1233,10 +938,10 @@
         <v>1020004</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
@@ -1247,10 +952,10 @@
         <v>1020005</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -1261,10 +966,10 @@
         <v>1020006</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -1275,10 +980,10 @@
         <v>1020007</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -1289,38 +994,38 @@
         <v>1020008</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>1040000</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>1040001</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -1331,10 +1036,10 @@
         <v>1040002</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
@@ -1345,10 +1050,10 @@
         <v>1040003</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
@@ -1359,10 +1064,10 @@
         <v>1040004</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
@@ -1373,10 +1078,10 @@
         <v>1040005</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -1387,10 +1092,10 @@
         <v>1040006</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
@@ -1401,10 +1106,10 @@
         <v>1040007</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
@@ -1415,10 +1120,10 @@
         <v>1040008</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
@@ -1429,10 +1134,10 @@
         <v>1040009</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
@@ -1443,10 +1148,10 @@
         <v>1040010</v>
       </c>
       <c r="D33" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
@@ -1457,10 +1162,10 @@
         <v>1040011</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
@@ -1471,10 +1176,10 @@
         <v>1040012</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
@@ -1485,10 +1190,10 @@
         <v>1040013</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64548B30-4E15-4899-8B2D-00D379FEB786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3864B8-CD56-49C9-8DA4-08A44D25C464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,9 +73,6 @@
     <t>星见雅</t>
   </si>
   <si>
-    <t>艾莲乔</t>
-  </si>
-  <si>
     <t>#Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,10 +177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>艾莲乔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲乔_普通攻击_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -259,6 +252,18 @@
   </si>
   <si>
     <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲_普通攻击_冰刃浪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲_普通攻击_霜降</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -653,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="24.125" customWidth="1"/>
@@ -669,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -681,7 +686,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -698,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="2"/>
@@ -721,29 +726,29 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>1010000</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I5" s="1"/>
       <c r="K5" s="3"/>
@@ -756,10 +761,10 @@
         <v>1010001</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I6" s="1"/>
       <c r="K6" s="2"/>
@@ -772,10 +777,10 @@
         <v>1010002</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1"/>
       <c r="K7" s="2"/>
@@ -788,10 +793,10 @@
         <v>1010003</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -802,10 +807,10 @@
         <v>1010004</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9" s="1"/>
       <c r="K9" s="2"/>
@@ -818,10 +823,10 @@
         <v>1010005</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K10" s="2"/>
     </row>
@@ -833,10 +838,10 @@
         <v>1010006</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K11" s="2"/>
     </row>
@@ -848,10 +853,10 @@
         <v>1010007</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12" s="1"/>
       <c r="K12" s="2"/>
@@ -864,25 +869,25 @@
         <v>1010008</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>1020000</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G14" s="1"/>
       <c r="K14" s="2"/>
@@ -895,10 +900,10 @@
         <v>1020001</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K15" s="2"/>
     </row>
@@ -910,10 +915,10 @@
         <v>1020002</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -924,10 +929,10 @@
         <v>1020003</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -938,10 +943,10 @@
         <v>1020004</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
@@ -952,10 +957,10 @@
         <v>1020005</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -966,10 +971,10 @@
         <v>1020006</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -980,10 +985,10 @@
         <v>1020007</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -994,206 +999,234 @@
         <v>1020008</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C23">
         <v>1040000</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C24">
         <v>1040001</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C25">
         <v>1040002</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C26">
         <v>1040003</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C27">
         <v>1040004</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>1040005</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>1040006</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>1040007</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>1040008</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>1040009</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>1040010</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>1040011</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>1040012</v>
       </c>
       <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" t="s">
         <v>52</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>1040013</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37">
+        <v>1040014</v>
+      </c>
+      <c r="D37" t="s">
         <v>59</v>
+      </c>
+      <c r="F37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38">
+        <v>1040015</v>
+      </c>
+      <c r="D38" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3864B8-CD56-49C9-8DA4-08A44D25C464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411B7670-E19E-4493-8DEB-0137E1E19158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="62">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -233,28 +233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1</t>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1</t>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -264,6 +242,33 @@
   </si>
   <si>
     <t>艾莲_普通攻击_霜降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,None|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -748,7 +753,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I5" s="1"/>
       <c r="K5" s="3"/>
@@ -764,7 +769,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I6" s="1"/>
       <c r="K6" s="2"/>
@@ -780,7 +785,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I7" s="1"/>
       <c r="K7" s="2"/>
@@ -796,7 +801,7 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -810,7 +815,7 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" s="1"/>
       <c r="K9" s="2"/>
@@ -826,7 +831,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2"/>
     </row>
@@ -841,7 +846,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2"/>
     </row>
@@ -856,7 +861,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" s="1"/>
       <c r="K12" s="2"/>
@@ -872,7 +877,7 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K13" s="2"/>
     </row>
@@ -887,7 +892,7 @@
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G14" s="1"/>
       <c r="K14" s="2"/>
@@ -903,7 +908,7 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K15" s="2"/>
     </row>
@@ -918,7 +923,7 @@
         <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -932,7 +937,7 @@
         <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -946,7 +951,7 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
@@ -960,7 +965,7 @@
         <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -974,7 +979,7 @@
         <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -988,7 +993,7 @@
         <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -1002,12 +1007,12 @@
         <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>1040000</v>
@@ -1016,12 +1021,12 @@
         <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C24">
         <v>1040001</v>
@@ -1030,12 +1035,12 @@
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>1040002</v>
@@ -1044,12 +1049,12 @@
         <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>1040003</v>
@@ -1058,12 +1063,12 @@
         <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>1040004</v>
@@ -1072,12 +1077,12 @@
         <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>1040005</v>
@@ -1086,12 +1091,12 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>1040006</v>
@@ -1100,12 +1105,12 @@
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>1040007</v>
@@ -1114,12 +1119,12 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1040008</v>
@@ -1128,12 +1133,12 @@
         <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>1040009</v>
@@ -1142,12 +1147,12 @@
         <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C33">
         <v>1040010</v>
@@ -1156,12 +1161,12 @@
         <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C34">
         <v>1040011</v>
@@ -1170,12 +1175,12 @@
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C35">
         <v>1040012</v>
@@ -1184,12 +1189,12 @@
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C36">
         <v>1040013</v>
@@ -1198,35 +1203,35 @@
         <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>1040014</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C38">
         <v>1040015</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411B7670-E19E-4493-8DEB-0137E1E19158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B84650-CBDC-4F5F-B7F0-88BED72A3297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -242,10 +242,6 @@
   </si>
   <si>
     <t>艾莲_普通攻击_霜降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,None|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -753,7 +749,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I5" s="1"/>
       <c r="K5" s="3"/>
@@ -769,7 +765,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I6" s="1"/>
       <c r="K6" s="2"/>
@@ -785,7 +781,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I7" s="1"/>
       <c r="K7" s="2"/>
@@ -801,7 +797,7 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -815,7 +811,7 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1"/>
       <c r="K9" s="2"/>
@@ -831,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K10" s="2"/>
     </row>
@@ -846,7 +842,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11" s="2"/>
     </row>
@@ -861,7 +857,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="1"/>
       <c r="K12" s="2"/>
@@ -877,7 +873,7 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K13" s="2"/>
     </row>
@@ -892,7 +888,7 @@
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="1"/>
       <c r="K14" s="2"/>
@@ -908,7 +904,7 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K15" s="2"/>
     </row>
@@ -923,7 +919,7 @@
         <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -937,7 +933,7 @@
         <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -951,7 +947,7 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
@@ -965,7 +961,7 @@
         <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -979,7 +975,7 @@
         <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -993,7 +989,7 @@
         <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -1007,7 +1003,7 @@
         <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -1021,7 +1017,7 @@
         <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -1035,7 +1031,7 @@
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -1049,7 +1045,7 @@
         <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
@@ -1063,7 +1059,7 @@
         <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
@@ -1077,7 +1073,7 @@
         <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
@@ -1091,7 +1087,7 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -1105,7 +1101,7 @@
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
@@ -1119,7 +1115,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
@@ -1133,7 +1129,7 @@
         <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
@@ -1147,7 +1143,7 @@
         <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
@@ -1161,7 +1157,7 @@
         <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
@@ -1175,7 +1171,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
@@ -1189,7 +1185,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
@@ -1203,7 +1199,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
@@ -1217,7 +1213,7 @@
         <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
@@ -1231,7 +1227,7 @@
         <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
